--- a/output/roomself_excel/2079.xlsx
+++ b/output/roomself_excel/2079.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7728</v>
+        <v>77800</v>
       </c>
       <c r="D2" t="n">
-        <v>724</v>
+        <v>2356</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6336</v>
+        <v>77600</v>
       </c>
       <c r="D3" t="n">
-        <v>652</v>
+        <v>2352</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6656</v>
+        <v>141960</v>
       </c>
       <c r="D4" t="n">
-        <v>544</v>
+        <v>3016</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6696</v>
+        <v>143540</v>
       </c>
       <c r="D5" t="n">
-        <v>680</v>
+        <v>3032</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>317971</v>
+        <v>72388</v>
       </c>
       <c r="D6" t="n">
-        <v>6192</v>
+        <v>2284</v>
       </c>
       <c r="E6" t="n">
-        <v>1031</v>
+        <v>400</v>
       </c>
       <c r="F6" t="n">
-        <v>603</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>319405</v>
+        <v>71132</v>
       </c>
       <c r="D7" t="n">
-        <v>6204</v>
+        <v>2268</v>
       </c>
       <c r="E7" t="n">
-        <v>1030</v>
+        <v>398</v>
       </c>
       <c r="F7" t="n">
-        <v>604</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>220563</v>
+        <v>87724</v>
       </c>
       <c r="D8" t="n">
-        <v>3824</v>
+        <v>2432</v>
       </c>
       <c r="E8" t="n">
-        <v>604</v>
+        <v>395</v>
       </c>
       <c r="F8" t="n">
-        <v>436</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>219007</v>
+        <v>83581</v>
       </c>
       <c r="D9" t="n">
-        <v>3808</v>
+        <v>2372</v>
       </c>
       <c r="E9" t="n">
-        <v>563</v>
+        <v>373</v>
       </c>
       <c r="F9" t="n">
-        <v>436</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26838</v>
+        <v>76962</v>
       </c>
       <c r="D10" t="n">
-        <v>1324</v>
+        <v>2228</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26696</v>
+        <v>77470</v>
       </c>
       <c r="D11" t="n">
-        <v>1320</v>
+        <v>2236</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>78151</v>
+        <v>33488</v>
       </c>
       <c r="D12" t="n">
-        <v>3612</v>
+        <v>1464</v>
       </c>
       <c r="E12" t="n">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33488</v>
+        <v>33672</v>
       </c>
       <c r="D13" t="n">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33672</v>
+        <v>28728</v>
       </c>
       <c r="D14" t="n">
-        <v>1468</v>
+        <v>1364</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>78182</v>
+        <v>28576</v>
       </c>
       <c r="D15" t="n">
-        <v>3600</v>
+        <v>1360</v>
       </c>
       <c r="E15" t="n">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>28728</v>
+        <v>98265</v>
       </c>
       <c r="D16" t="n">
-        <v>1364</v>
+        <v>3844</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28576</v>
+        <v>98211</v>
       </c>
       <c r="D17" t="n">
-        <v>1360</v>
+        <v>3832</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>72388</v>
+        <v>26134</v>
       </c>
       <c r="D18" t="n">
-        <v>2284</v>
+        <v>1300</v>
       </c>
       <c r="E18" t="n">
-        <v>400</v>
+        <v>141</v>
       </c>
       <c r="F18" t="n">
-        <v>245</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>71132</v>
+        <v>25665</v>
       </c>
       <c r="D19" t="n">
-        <v>2268</v>
+        <v>1288</v>
       </c>
       <c r="E19" t="n">
-        <v>398</v>
+        <v>144</v>
       </c>
       <c r="F19" t="n">
-        <v>247</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>87724</v>
+        <v>16926</v>
       </c>
       <c r="D20" t="n">
-        <v>2432</v>
+        <v>1100</v>
       </c>
       <c r="E20" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>16926</v>
+        <v>17019</v>
       </c>
       <c r="D21" t="n">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17019</v>
+        <v>43674</v>
       </c>
       <c r="D22" t="n">
-        <v>1104</v>
+        <v>1700</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -928,20 +928,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>83581</v>
+        <v>42670</v>
       </c>
       <c r="D23" t="n">
-        <v>2372</v>
+        <v>1684</v>
       </c>
       <c r="E23" t="n">
-        <v>373</v>
+        <v>251</v>
       </c>
       <c r="F23" t="n">
-        <v>256</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -950,20 +950,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>76962</v>
+        <v>7728</v>
       </c>
       <c r="D24" t="n">
-        <v>2228</v>
+        <v>724</v>
       </c>
       <c r="E24" t="n">
-        <v>303</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -972,20 +972,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>77470</v>
+        <v>6336</v>
       </c>
       <c r="D25" t="n">
-        <v>2236</v>
+        <v>652</v>
       </c>
       <c r="E25" t="n">
-        <v>305</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>44694</v>
+        <v>6656</v>
       </c>
       <c r="D26" t="n">
-        <v>1700</v>
+        <v>544</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>43758</v>
+        <v>6696</v>
       </c>
       <c r="D27" t="n">
-        <v>1684</v>
+        <v>680</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1038,20 +1038,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26134</v>
+        <v>220563</v>
       </c>
       <c r="D28" t="n">
-        <v>1300</v>
+        <v>3824</v>
       </c>
       <c r="E28" t="n">
-        <v>306</v>
+        <v>604</v>
       </c>
       <c r="F28" t="n">
-        <v>142</v>
+        <v>436</v>
       </c>
     </row>
     <row r="29">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25665</v>
+        <v>219007</v>
       </c>
       <c r="D29" t="n">
-        <v>1288</v>
+        <v>3808</v>
       </c>
       <c r="E29" t="n">
-        <v>306</v>
+        <v>563</v>
       </c>
       <c r="F29" t="n">
-        <v>145</v>
+        <v>436</v>
       </c>
     </row>
     <row r="30">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>43674</v>
+        <v>26838</v>
       </c>
       <c r="D30" t="n">
-        <v>1700</v>
+        <v>1324</v>
       </c>
       <c r="E30" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1104,20 +1104,108 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>42670</v>
+        <v>26696</v>
       </c>
       <c r="D31" t="n">
+        <v>1320</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>78151</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3612</v>
+      </c>
+      <c r="E32" t="n">
+        <v>181</v>
+      </c>
+      <c r="F32" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>78182</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>44694</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>43758</v>
+      </c>
+      <c r="D35" t="n">
         <v>1684</v>
       </c>
-      <c r="E31" t="n">
-        <v>251</v>
-      </c>
-      <c r="F31" t="n">
-        <v>31</v>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/2079.xlsx
+++ b/output/roomself_excel/2079.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>2356</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>200</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>39</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +543,23 @@
       <c r="D3" t="n">
         <v>2352</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>200</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>39</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +576,31 @@
       <c r="D4" t="n">
         <v>3016</v>
       </c>
-      <c r="E4" t="n">
-        <v>429</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>403</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>390</v>
+      </c>
+      <c r="J4" t="n">
+        <v>39</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +617,31 @@
       <c r="D5" t="n">
         <v>3032</v>
       </c>
-      <c r="E5" t="n">
-        <v>428</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>404</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="G5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>389</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +658,31 @@
       <c r="D6" t="n">
         <v>2284</v>
       </c>
-      <c r="E6" t="n">
-        <v>400</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>245</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="G6" t="n">
+        <v>35</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>210</v>
+      </c>
+      <c r="J6" t="n">
+        <v>39</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +699,31 @@
       <c r="D7" t="n">
         <v>2268</v>
       </c>
-      <c r="E7" t="n">
-        <v>398</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>247</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="G7" t="n">
+        <v>39</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>208</v>
+      </c>
+      <c r="J7" t="n">
+        <v>39</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +740,31 @@
       <c r="D8" t="n">
         <v>2432</v>
       </c>
-      <c r="E8" t="n">
-        <v>395</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>287</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="G8" t="n">
+        <v>37</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>250</v>
+      </c>
+      <c r="J8" t="n">
+        <v>37</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +781,38 @@
       <c r="D9" t="n">
         <v>2372</v>
       </c>
-      <c r="E9" t="n">
-        <v>373</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>256</v>
+        <v>350</v>
+      </c>
+      <c r="G9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>18</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>243</v>
+      </c>
+      <c r="M9" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +830,23 @@
       <c r="D10" t="n">
         <v>2228</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>303</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>37</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +863,23 @@
       <c r="D11" t="n">
         <v>2236</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>305</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>37</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +896,15 @@
       <c r="D12" t="n">
         <v>1464</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +921,15 @@
       <c r="D13" t="n">
         <v>1468</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +946,15 @@
       <c r="D14" t="n">
         <v>1364</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +971,15 @@
       <c r="D15" t="n">
         <v>1360</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +996,23 @@
       <c r="D16" t="n">
         <v>3844</v>
       </c>
-      <c r="E16" t="n">
-        <v>191</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
+        <v>182</v>
+      </c>
+      <c r="G16" t="n">
         <v>35</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1029,23 @@
       <c r="D17" t="n">
         <v>3832</v>
       </c>
-      <c r="E17" t="n">
-        <v>193</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
+        <v>184</v>
+      </c>
+      <c r="G17" t="n">
         <v>39</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1062,23 @@
       <c r="D18" t="n">
         <v>1300</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>141</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>39</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1095,23 @@
       <c r="D19" t="n">
         <v>1288</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>144</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>39</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1128,15 @@
       <c r="D20" t="n">
         <v>1100</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1153,15 @@
       <c r="D21" t="n">
         <v>1104</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1178,31 @@
       <c r="D22" t="n">
         <v>1700</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>251</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>32</v>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>174</v>
+      </c>
+      <c r="J22" t="n">
+        <v>32</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1219,31 @@
       <c r="D23" t="n">
         <v>1684</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>251</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>31</v>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>170</v>
+      </c>
+      <c r="J23" t="n">
+        <v>32</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1260,15 @@
       <c r="D24" t="n">
         <v>724</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1285,15 @@
       <c r="D25" t="n">
         <v>652</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1310,15 @@
       <c r="D26" t="n">
         <v>544</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1335,15 @@
       <c r="D27" t="n">
         <v>680</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,11 +1360,38 @@
       <c r="D28" t="n">
         <v>3824</v>
       </c>
-      <c r="E28" t="n">
-        <v>604</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>436</v>
+        <v>567</v>
+      </c>
+      <c r="G28" t="n">
+        <v>37</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>389</v>
+      </c>
+      <c r="J28" t="n">
+        <v>37</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>10</v>
+      </c>
+      <c r="M28" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="29">
@@ -1069,11 +1409,38 @@
       <c r="D29" t="n">
         <v>3808</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>563</v>
       </c>
-      <c r="F29" t="n">
-        <v>436</v>
+      <c r="G29" t="n">
+        <v>37</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>389</v>
+      </c>
+      <c r="J29" t="n">
+        <v>35</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>10</v>
+      </c>
+      <c r="M29" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -1091,12 +1458,15 @@
       <c r="D30" t="n">
         <v>1324</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1113,12 +1483,15 @@
       <c r="D31" t="n">
         <v>1320</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1135,12 +1508,23 @@
       <c r="D32" t="n">
         <v>3612</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>181</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>37</v>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1157,12 +1541,23 @@
       <c r="D33" t="n">
         <v>3600</v>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="G33" t="n">
+        <v>35</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1179,12 +1574,15 @@
       <c r="D34" t="n">
         <v>1700</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1201,12 +1599,15 @@
       <c r="D35" t="n">
         <v>1684</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/2079.xlsx
+++ b/output/roomself_excel/2079.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:Y35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,66 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
         </is>
       </c>
     </row>
@@ -527,6 +587,30 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>39</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -560,6 +644,30 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>39</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -601,6 +709,54 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>39</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>97</v>
+      </c>
+      <c r="U4" t="n">
+        <v>39</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>146</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -642,6 +798,42 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>39</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>92</v>
+      </c>
+      <c r="U5" t="n">
+        <v>39</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -683,6 +875,30 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>149</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>39</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -724,6 +940,42 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>39</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>103</v>
+      </c>
+      <c r="U7" t="n">
+        <v>39</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -765,6 +1017,30 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>37</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -812,6 +1088,54 @@
         <v>243</v>
       </c>
       <c r="M9" t="n">
+        <v>37</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>14</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>49</v>
+      </c>
+      <c r="U9" t="n">
+        <v>35</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>104</v>
+      </c>
+      <c r="Y9" t="n">
         <v>37</v>
       </c>
     </row>
@@ -847,6 +1171,30 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>37</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -880,6 +1228,30 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>37</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -905,6 +1277,18 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -930,6 +1314,18 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -955,6 +1351,18 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -980,6 +1388,18 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1013,6 +1433,18 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1046,6 +1478,30 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>39</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1079,6 +1535,30 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>39</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1112,6 +1592,30 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>39</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1137,6 +1641,18 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1162,6 +1678,18 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1203,6 +1731,30 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>32</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1244,6 +1796,30 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>31</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1269,6 +1845,18 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1294,6 +1882,18 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1319,6 +1919,18 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1344,6 +1956,18 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1393,6 +2017,18 @@
       <c r="M28" t="n">
         <v>10</v>
       </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1442,6 +2078,18 @@
       <c r="M29" t="n">
         <v>10</v>
       </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1467,6 +2115,18 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1492,6 +2152,18 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1525,6 +2197,30 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>37</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1558,6 +2254,30 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>35</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1583,6 +2303,18 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1608,6 +2340,18 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
